--- a/data/trans_orig/P39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39A-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012 (tasa de respuesta: 96,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62128</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46467</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>81553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88878</t>
+          <t>89404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129986</t>
+          <t>129814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90323</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129579</t>
+          <t>128156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87027</t>
+          <t>87030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127305</t>
+          <t>127191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185354</t>
+          <t>185293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241944</t>
+          <t>242469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134206</t>
+          <t>134422</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180350</t>
+          <t>181472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175905</t>
+          <t>177979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>229303</t>
+          <t>228951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>324788</t>
+          <t>324230</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>393398</t>
+          <t>392626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87106</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129160</t>
+          <t>129018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166694</t>
+          <t>168545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219707</t>
+          <t>218212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265433</t>
+          <t>268916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334385</t>
+          <t>332815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398807</t>
+          <t>398336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458910</t>
+          <t>458251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>633285</t>
+          <t>635292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>702197</t>
+          <t>703174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1043268</t>
+          <t>1050703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140207</t>
+          <t>1135165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134675</t>
+          <t>134745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182858</t>
+          <t>183730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122977</t>
+          <t>122964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171624</t>
+          <t>173061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268904</t>
+          <t>273679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338718</t>
+          <t>337053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>352793</t>
+          <t>354509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424156</t>
+          <t>426353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285626</t>
+          <t>281776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349571</t>
+          <t>345944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655914</t>
+          <t>654392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>756762</t>
+          <t>749002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384811</t>
+          <t>378953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456411</t>
+          <t>451259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>311500</t>
+          <t>315115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>380017</t>
+          <t>385542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>709498</t>
+          <t>718098</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>808393</t>
+          <t>815498</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153886</t>
+          <t>153969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205392</t>
+          <t>206669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164684</t>
+          <t>162129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216427</t>
+          <t>213021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>334203</t>
+          <t>327674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>406835</t>
+          <t>404952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356847</t>
+          <t>359716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>426162</t>
+          <t>432125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>427126</t>
+          <t>429561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>495720</t>
+          <t>501138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>805579</t>
+          <t>802187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>906436</t>
+          <t>905739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58299</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64246</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101531</t>
+          <t>103237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>74536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110967</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66654</t>
+          <t>66415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149129</t>
+          <t>147489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195898</t>
+          <t>196556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89732</t>
+          <t>91301</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>129221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91158</t>
+          <t>90553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>130514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>192854</t>
+          <t>190740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>245078</t>
+          <t>246648</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67789</t>
+          <t>66955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>54185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73645</t>
+          <t>75389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>111601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>82786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121625</t>
+          <t>120733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102960</t>
+          <t>103890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142296</t>
+          <t>143816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196488</t>
+          <t>196395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250570</t>
+          <t>250606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>218206</t>
+          <t>215797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>279221</t>
+          <t>279339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217703</t>
+          <t>220574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281080</t>
+          <t>282150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>452147</t>
+          <t>453154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>539798</t>
+          <t>539825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545691</t>
+          <t>545747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>636059</t>
+          <t>635538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>458621</t>
+          <t>461068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>543154</t>
+          <t>546062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1024575</t>
+          <t>1033865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1146514</t>
+          <t>1156568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>630534</t>
+          <t>631158</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>725990</t>
+          <t>725346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>610563</t>
+          <t>611929</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>709800</t>
+          <t>703134</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1272000</t>
+          <t>1271109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1397220</t>
+          <t>1409503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302021</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>374428</t>
+          <t>376526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>382426</t>
+          <t>381860</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>459203</t>
+          <t>458151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>707291</t>
+          <t>708531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>812216</t>
+          <t>811207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>871248</t>
+          <t>870139</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>980026</t>
+          <t>972593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1195630</t>
+          <t>1194521</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1304906</t>
+          <t>1315166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2099972</t>
+          <t>2094666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2256644</t>
+          <t>2251380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016 (tasa de respuesta: 96,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>52964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84610</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>37369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97709</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139351</t>
+          <t>142569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103206</t>
+          <t>102632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142678</t>
+          <t>142913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>122451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170985</t>
+          <t>168316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>238062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>294205</t>
+          <t>298691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>164154</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>208528</t>
+          <t>206848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207700</t>
+          <t>205821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260469</t>
+          <t>259224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>383307</t>
+          <t>382231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>454751</t>
+          <t>454511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86447</t>
+          <t>86892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121765</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162055</t>
+          <t>161531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>211890</t>
+          <t>210638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259128</t>
+          <t>258955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319222</t>
+          <t>320268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161175</t>
+          <t>156068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204516</t>
+          <t>203926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280117</t>
+          <t>283032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342432</t>
+          <t>343669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>451288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>533349</t>
+          <t>529642</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175005</t>
+          <t>172853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228148</t>
+          <t>230352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,47 +4388,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>183255</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>156864</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>207865</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>10,91%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>183255</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>160137</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>213065</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351015</t>
+          <t>347965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424453</t>
+          <t>424598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423423</t>
+          <t>420386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497097</t>
+          <t>495351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>426763</t>
+          <t>431812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501856</t>
+          <t>504104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,47 +4536,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>926692</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>876209</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>981311</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>28,22%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>26,68%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>29,88%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>926692</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>875790</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>982962</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415307</t>
+          <t>414402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486554</t>
+          <t>492591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>424674</t>
+          <t>423664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>499774</t>
+          <t>499170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>859106</t>
+          <t>858874</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>960673</t>
+          <t>960760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182169</t>
+          <t>181624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238497</t>
+          <t>242016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182186</t>
+          <t>180425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235646</t>
+          <t>237119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381859</t>
+          <t>380867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459719</t>
+          <t>458621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252263</t>
+          <t>252066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316632</t>
+          <t>314975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328774</t>
+          <t>327527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397795</t>
+          <t>397260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>598282</t>
+          <t>599678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>695541</t>
+          <t>695174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>44646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76632</t>
+          <t>75329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60226</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>87872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129280</t>
+          <t>127117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105324</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144978</t>
+          <t>144830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121741</t>
+          <t>118969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162091</t>
+          <t>159743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>238133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>291862</t>
+          <t>297531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98015</t>
+          <t>97737</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133767</t>
+          <t>136833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106873</t>
+          <t>106871</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144274</t>
+          <t>145073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>214773</t>
+          <t>215676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269797</t>
+          <t>266677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33532</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>48257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>79451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90908</t>
+          <t>93575</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>134082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80852</t>
+          <t>78604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118035</t>
+          <t>117751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110716</t>
+          <t>112528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>165244</t>
+          <t>164212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216446</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>293881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367079</t>
+          <t>362741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>248695</t>
+          <t>250637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315407</t>
+          <t>314930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>559735</t>
+          <t>563425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>656058</t>
+          <t>656780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>664393</t>
+          <t>660364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>752297</t>
+          <t>753255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>704371</t>
+          <t>706115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801571</t>
+          <t>806688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1393672</t>
+          <t>1395156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1524699</t>
+          <t>1532696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>703525</t>
+          <t>702449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>794294</t>
+          <t>796490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>764442</t>
+          <t>762971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>871480</t>
+          <t>867749</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1495885</t>
+          <t>1503147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1631823</t>
+          <t>1634160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>329056</t>
+          <t>326252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>398269</t>
+          <t>401284</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>420868</t>
+          <t>421821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>499382</t>
+          <t>497508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>768770</t>
+          <t>764125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>882575</t>
+          <t>872139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>518541</t>
+          <t>516319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>602177</t>
+          <t>606292</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>717297</t>
+          <t>714656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811460</t>
+          <t>812187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1267668</t>
+          <t>1257800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1393241</t>
+          <t>1396037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023 (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>44824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>49881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76732</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>70049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101237</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>90524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119257</t>
+          <t>118522</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169289</t>
+          <t>166274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214426</t>
+          <t>210308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91387</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123838</t>
+          <t>123952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156977</t>
+          <t>158187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190704</t>
+          <t>191133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>259874</t>
+          <t>258859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308229</t>
+          <t>308098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86068</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119969</t>
+          <t>117788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145686</t>
+          <t>145660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178250</t>
+          <t>179967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240716</t>
+          <t>240965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289133</t>
+          <t>288714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119432</t>
+          <t>118911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154418</t>
+          <t>154242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213095</t>
+          <t>211882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251302</t>
+          <t>250158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341243</t>
+          <t>343554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393387</t>
+          <t>394183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129485</t>
+          <t>126749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186065</t>
+          <t>182742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114305</t>
+          <t>115695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195523</t>
+          <t>197942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264798</t>
+          <t>261829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>364581</t>
+          <t>362430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399172</t>
+          <t>396949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>483905</t>
+          <t>483296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465469</t>
+          <t>464059</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1053726</t>
+          <t>1053167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>898892</t>
+          <t>894931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1564556</t>
+          <t>1546613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434992</t>
+          <t>436259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>518081</t>
+          <t>518660</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343940</t>
+          <t>343569</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>574848</t>
+          <t>581616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>779754</t>
+          <t>788334</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1063162</t>
+          <t>1066377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232238</t>
+          <t>233981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296589</t>
+          <t>294713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158678</t>
+          <t>172934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286032</t>
+          <t>288763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>413404</t>
+          <t>416465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564393</t>
+          <t>562147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264938</t>
+          <t>264552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>329040</t>
+          <t>328931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246443</t>
+          <t>245274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427509</t>
+          <t>429482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>547297</t>
+          <t>548658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724886</t>
+          <t>728693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52822</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67564</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101653</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129945</t>
+          <t>131320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176750</t>
+          <t>173265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113273</t>
+          <t>114182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>146910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251632</t>
+          <t>251824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310683</t>
+          <t>307245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149019</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>196810</t>
+          <t>197966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153925</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>192392</t>
+          <t>190700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317083</t>
+          <t>316380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>377726</t>
+          <t>375637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>72327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109008</t>
+          <t>109251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75886</t>
+          <t>77688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106251</t>
+          <t>106649</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156989</t>
+          <t>156062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>204309</t>
+          <t>200429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97921</t>
+          <t>98947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136497</t>
+          <t>136388</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137498</t>
+          <t>135945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174796</t>
+          <t>173188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246029</t>
+          <t>244692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296702</t>
+          <t>299582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192870</t>
+          <t>189989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>263170</t>
+          <t>258642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189620</t>
+          <t>194760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>271692</t>
+          <t>272597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405623</t>
+          <t>407610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>509364</t>
+          <t>517189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618556</t>
+          <t>628622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>724419</t>
+          <t>730158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>692513</t>
+          <t>687808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1408205</t>
+          <t>1303958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1358561</t>
+          <t>1358696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1986561</t>
+          <t>2087173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>705166</t>
+          <t>705831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>803282</t>
+          <t>810562</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>673421</t>
+          <t>666286</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>927222</t>
+          <t>933507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1425281</t>
+          <t>1402348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1698672</t>
+          <t>1692550</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>415105</t>
+          <t>415449</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>495510</t>
+          <t>496524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>379824</t>
+          <t>407967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>548504</t>
+          <t>551554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>843145</t>
+          <t>837469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1014337</t>
+          <t>1013896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>510032</t>
+          <t>501736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>589638</t>
+          <t>587143</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>582714</t>
+          <t>608606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819104</t>
+          <t>823574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1153821</t>
+          <t>1147088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1380024</t>
+          <t>1375235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39A-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48053</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>79980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89404</t>
+          <t>88362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>129165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128156</t>
+          <t>128792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87030</t>
+          <t>84395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127191</t>
+          <t>127488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185293</t>
+          <t>185851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242469</t>
+          <t>241274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134422</t>
+          <t>131843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181472</t>
+          <t>179776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177979</t>
+          <t>178265</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>228951</t>
+          <t>228683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>324230</t>
+          <t>324770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>392626</t>
+          <t>393921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>86467</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>127605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168545</t>
+          <t>165506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218212</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268916</t>
+          <t>265503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>332815</t>
+          <t>333055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398336</t>
+          <t>397643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458251</t>
+          <t>457285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>635292</t>
+          <t>632690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>703174</t>
+          <t>705321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1050703</t>
+          <t>1043515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1135165</t>
+          <t>1139280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134745</t>
+          <t>133160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183730</t>
+          <t>183663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122964</t>
+          <t>123778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173061</t>
+          <t>173404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273679</t>
+          <t>271509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337053</t>
+          <t>344135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354509</t>
+          <t>352812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426353</t>
+          <t>423783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>281776</t>
+          <t>283487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345944</t>
+          <t>348040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654392</t>
+          <t>658463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749002</t>
+          <t>754067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>378953</t>
+          <t>381237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>451259</t>
+          <t>454170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>315115</t>
+          <t>314640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>385542</t>
+          <t>382086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>718098</t>
+          <t>710261</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>815498</t>
+          <t>814031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153969</t>
+          <t>152996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206669</t>
+          <t>207877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162129</t>
+          <t>163203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213021</t>
+          <t>217770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327674</t>
+          <t>330293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404952</t>
+          <t>407700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359716</t>
+          <t>356133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432125</t>
+          <t>429827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429561</t>
+          <t>426528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501138</t>
+          <t>500621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>802187</t>
+          <t>807477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>905739</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59880</t>
+          <t>57095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>54090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>66642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103237</t>
+          <t>102681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74536</t>
+          <t>75978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109400</t>
+          <t>109307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66415</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99931</t>
+          <t>99131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147489</t>
+          <t>148104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196556</t>
+          <t>196604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91301</t>
+          <t>91139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129221</t>
+          <t>128789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90553</t>
+          <t>90420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130514</t>
+          <t>128776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190740</t>
+          <t>189383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>246648</t>
+          <t>243591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66955</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54185</t>
+          <t>55244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75389</t>
+          <t>74303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111601</t>
+          <t>114665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82786</t>
+          <t>83940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120733</t>
+          <t>122278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103890</t>
+          <t>103050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>141976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196395</t>
+          <t>198189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250606</t>
+          <t>251995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>215797</t>
+          <t>218638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>279339</t>
+          <t>280390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,82 +2793,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>247586</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>215944</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>281016</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>494976</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>455155</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>539122</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>247586</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>220574</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>282150</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>494976</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>453154</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>539825</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545747</t>
+          <t>546081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>635538</t>
+          <t>634453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>461068</t>
+          <t>460860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546062</t>
+          <t>544442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1033865</t>
+          <t>1031665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1156568</t>
+          <t>1149089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>631158</t>
+          <t>631174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>725346</t>
+          <t>726973</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>611929</t>
+          <t>610420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>703134</t>
+          <t>700911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1271109</t>
+          <t>1272122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1409503</t>
+          <t>1403272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>300627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>376526</t>
+          <t>374507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>381860</t>
+          <t>385236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>458151</t>
+          <t>463961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>708531</t>
+          <t>707868</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>811207</t>
+          <t>810289</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>870139</t>
+          <t>873077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>972593</t>
+          <t>973121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1194521</t>
+          <t>1197191</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1315166</t>
+          <t>1303529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2094666</t>
+          <t>2100412</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2251380</t>
+          <t>2245398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>53702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83151</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37369</t>
+          <t>37730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>66521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97694</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>138734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102632</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142913</t>
+          <t>141627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122451</t>
+          <t>122492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168316</t>
+          <t>166908</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238062</t>
+          <t>236948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298691</t>
+          <t>299280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164154</t>
+          <t>163901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206848</t>
+          <t>206878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205821</t>
+          <t>206272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>259224</t>
+          <t>259104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>382231</t>
+          <t>383977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>454511</t>
+          <t>455319</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86892</t>
+          <t>88188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>122659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>159757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210638</t>
+          <t>210166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258955</t>
+          <t>257677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320268</t>
+          <t>322620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156068</t>
+          <t>158271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203926</t>
+          <t>201499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283032</t>
+          <t>279515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>343669</t>
+          <t>339649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>451288</t>
+          <t>451947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>529642</t>
+          <t>529905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172853</t>
+          <t>175708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230352</t>
+          <t>229825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>159552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207865</t>
+          <t>211240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347965</t>
+          <t>350821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424598</t>
+          <t>430871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420386</t>
+          <t>425784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495351</t>
+          <t>498104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431812</t>
+          <t>431831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>504104</t>
+          <t>504920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876209</t>
+          <t>871950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>981311</t>
+          <t>977168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>414402</t>
+          <t>415641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>492591</t>
+          <t>493465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>423664</t>
+          <t>422545</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>499170</t>
+          <t>496544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>858874</t>
+          <t>853440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>960760</t>
+          <t>961337</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>184710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242016</t>
+          <t>238726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180425</t>
+          <t>180965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237119</t>
+          <t>235677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380867</t>
+          <t>380944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>458621</t>
+          <t>459993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252066</t>
+          <t>249876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314975</t>
+          <t>312411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>330048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397260</t>
+          <t>399527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>599678</t>
+          <t>601225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>695174</t>
+          <t>691253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44646</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75329</t>
+          <t>76681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87872</t>
+          <t>86999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127117</t>
+          <t>127222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105637</t>
+          <t>103175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144830</t>
+          <t>144064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118969</t>
+          <t>120500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159743</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238133</t>
+          <t>235085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297531</t>
+          <t>293706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97737</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136833</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106871</t>
+          <t>105676</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145073</t>
+          <t>143886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215676</t>
+          <t>212858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>266677</t>
+          <t>268919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35638</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64207</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48257</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79451</t>
+          <t>80540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93575</t>
+          <t>92358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134082</t>
+          <t>134723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117751</t>
+          <t>117456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>76817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112528</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164212</t>
+          <t>165512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>213104</t>
+          <t>215174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293881</t>
+          <t>292817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>362741</t>
+          <t>364304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250637</t>
+          <t>250482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314930</t>
+          <t>316240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>563425</t>
+          <t>558933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>656780</t>
+          <t>657609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>660364</t>
+          <t>661377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>753255</t>
+          <t>752784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>706115</t>
+          <t>705900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>806688</t>
+          <t>799687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1395156</t>
+          <t>1393993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1532696</t>
+          <t>1526734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>702449</t>
+          <t>702332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>796490</t>
+          <t>798733</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>762971</t>
+          <t>770348</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>867749</t>
+          <t>868372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1503147</t>
+          <t>1502448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1634160</t>
+          <t>1636557</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>326252</t>
+          <t>322577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>401284</t>
+          <t>397574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>421821</t>
+          <t>417713</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>497508</t>
+          <t>497908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>764125</t>
+          <t>770522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>872139</t>
+          <t>879226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>516319</t>
+          <t>519032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>606292</t>
+          <t>606497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714656</t>
+          <t>716011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>812187</t>
+          <t>817680</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1257800</t>
+          <t>1255357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1396037</t>
+          <t>1386955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>37015</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>50549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>43274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>70170</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>56233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77041</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85285</t>
+          <t>94417</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70049</t>
+          <t>77391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102269</t>
+          <t>111547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>103740</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>96549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118522</t>
+          <t>126038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>189025</t>
+          <t>205897</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166274</t>
+          <t>185322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210308</t>
+          <t>230494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107923</t>
+          <t>120500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92113</t>
+          <t>103344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123952</t>
+          <t>138895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174830</t>
+          <t>197328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158187</t>
+          <t>180297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>191133</t>
+          <t>216836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>282753</t>
+          <t>317828</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>258859</t>
+          <t>293636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308098</t>
+          <t>344099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>101167</t>
+          <t>110457</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85183</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117788</t>
+          <t>128876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>162669</t>
+          <t>178162</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145660</t>
+          <t>161549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>196250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>263836</t>
+          <t>288620</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240965</t>
+          <t>264153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288714</t>
+          <t>314400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136346</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>125304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154242</t>
+          <t>161059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>230455</t>
+          <t>242170</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211882</t>
+          <t>222950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250158</t>
+          <t>261032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>366801</t>
+          <t>385684</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343554</t>
+          <t>359885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394183</t>
+          <t>410559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>462760</t>
+          <t>505903</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>462760</t>
+          <t>505903</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>462760</t>
+          <t>505903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>702349</t>
+          <t>762296</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>702349</t>
+          <t>762296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>702349</t>
+          <t>762296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1165109</t>
+          <t>1268198</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1165109</t>
+          <t>1268198</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1165109</t>
+          <t>1268198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170494</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126749</t>
+          <t>141657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182742</t>
+          <t>202997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,67 +7362,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165245</t>
+          <t>178128</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115695</t>
+          <t>153028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197942</t>
+          <t>201512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>348622</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>311957</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>387423</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>8,66%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>320103</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>261829</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>362430</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>437064</t>
+          <t>475362</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396949</t>
+          <t>433070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>483296</t>
+          <t>516482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>631328</t>
+          <t>473536</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464059</t>
+          <t>439846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1053167</t>
+          <t>511113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1068392</t>
+          <t>948898</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>894931</t>
+          <t>891922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1546613</t>
+          <t>1003253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>475803</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>436259</t>
+          <t>462491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>518660</t>
+          <t>543114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>495012</t>
+          <t>511724</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343569</t>
+          <t>481598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>581616</t>
+          <t>548846</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>970815</t>
+          <t>1011369</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>788334</t>
+          <t>956912</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1066377</t>
+          <t>1067930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>263791</t>
+          <t>285821</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233981</t>
+          <t>254342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294713</t>
+          <t>323100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>246066</t>
+          <t>269813</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172934</t>
+          <t>244266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288763</t>
+          <t>298518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>509857</t>
+          <t>555634</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416465</t>
+          <t>516753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>562147</t>
+          <t>596684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -7779,27 +7779,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>294334</t>
+          <t>320501</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264552</t>
+          <t>286080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328931</t>
+          <t>354382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>369563</t>
+          <t>418546</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245274</t>
+          <t>387467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>429482</t>
+          <t>451825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>663896</t>
+          <t>739047</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>548658</t>
+          <t>694392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728693</t>
+          <t>788966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1625850</t>
+          <t>1751823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1625850</t>
+          <t>1751823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1625850</t>
+          <t>1751823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1907214</t>
+          <t>1851746</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1907214</t>
+          <t>1851746</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1907214</t>
+          <t>1851746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3533063</t>
+          <t>3603569</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3533063</t>
+          <t>3603569</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3533063</t>
+          <t>3603569</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>42789</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53180</t>
+          <t>59519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44938</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58331</t>
+          <t>62464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>82830</t>
+          <t>90782</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>109249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>151607</t>
+          <t>164687</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131320</t>
+          <t>141312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173265</t>
+          <t>191715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128926</t>
+          <t>144862</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>114182</t>
+          <t>126688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146910</t>
+          <t>164532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>280532</t>
+          <t>309549</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251824</t>
+          <t>279500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307245</t>
+          <t>339510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>171295</t>
+          <t>189553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>163826</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197966</t>
+          <t>216524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>172278</t>
+          <t>190233</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>170794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190700</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>343573</t>
+          <t>379787</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316380</t>
+          <t>349070</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>375637</t>
+          <t>417641</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88387</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72327</t>
+          <t>80705</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109251</t>
+          <t>117609</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>90627</t>
+          <t>104138</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77688</t>
+          <t>89069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106649</t>
+          <t>122313</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>179014</t>
+          <t>202000</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156062</t>
+          <t>179603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200429</t>
+          <t>228166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>115713</t>
+          <t>129405</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98947</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136388</t>
+          <t>150972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>154917</t>
+          <t>172034</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>152998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173188</t>
+          <t>192528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>270630</t>
+          <t>301440</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244692</t>
+          <t>273749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299582</t>
+          <t>334960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>624297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>624297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>624297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>591685</t>
+          <t>659260</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>591685</t>
+          <t>659260</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>591685</t>
+          <t>659260</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1156578</t>
+          <t>1283557</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1156578</t>
+          <t>1283557</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1156578</t>
+          <t>1283557</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>224789</t>
+          <t>250298</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189989</t>
+          <t>219554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>258642</t>
+          <t>288231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>259275</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194760</t>
+          <t>231622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272597</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>465627</t>
+          <t>509573</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407610</t>
+          <t>465115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517189</t>
+          <t>551456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>673956</t>
+          <t>734467</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>628622</t>
+          <t>683994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>730158</t>
+          <t>787180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>863993</t>
+          <t>729878</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687808</t>
+          <t>683934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1303958</t>
+          <t>769782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1537949</t>
+          <t>1464345</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1358696</t>
+          <t>1391320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2087173</t>
+          <t>1528512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>755021</t>
+          <t>809699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>705831</t>
+          <t>762127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>810562</t>
+          <t>864429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>842118</t>
+          <t>899285</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>666286</t>
+          <t>859298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>933507</t>
+          <t>951605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1597140</t>
+          <t>1708983</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1402348</t>
+          <t>1649723</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1692550</t>
+          <t>1781382</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>453345</t>
+          <t>494140</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>415449</t>
+          <t>456341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>496524</t>
+          <t>535966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>499362</t>
+          <t>552113</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>407967</t>
+          <t>515568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>551554</t>
+          <t>589901</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>952707</t>
+          <t>1046253</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>837469</t>
+          <t>996162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1013896</t>
+          <t>1101377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -9143,17 +9143,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>546392</t>
+          <t>593420</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>501736</t>
+          <t>549494</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>587143</t>
+          <t>637972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>754935</t>
+          <t>832750</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>608606</t>
+          <t>786913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823574</t>
+          <t>874326</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1301327</t>
+          <t>1426170</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147088</t>
+          <t>1361647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1375235</t>
+          <t>1484605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2653503</t>
+          <t>2882023</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2653503</t>
+          <t>2882023</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2653503</t>
+          <t>2882023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3201247</t>
+          <t>3273301</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3201247</t>
+          <t>3273301</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3201247</t>
+          <t>3273301</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5854751</t>
+          <t>6155324</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5854751</t>
+          <t>6155324</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5854751</t>
+          <t>6155324</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
